--- a/fire_inspection_forms/003_fire_safety_inspection_checklist--fire_inspection_forms.xlsx
+++ b/fire_inspection_forms/003_fire_safety_inspection_checklist--fire_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -531,7 +531,7 @@
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -561,7 +561,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>fire_stations</t>
+          <t>fire_extinguishers</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Fire Stations</t>
+          <t>Fire Extinguishers</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -612,12 +612,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>fire_extinguishers</t>
+          <t>fire_hydrants</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fire Extinguishers</t>
+          <t>Fire Hydrants</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>fire_extinguishers</t>
+          <t>fire_alarm_system</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fire Extinguishers</t>
+          <t>Fire Alarm System</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,18 +658,18 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>fire_hydrants</t>
+          <t>emergency_exit_paths</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fire Hydrants</t>
+          <t>Emergency Exit Paths</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -681,35 +681,35 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>fire_hydrants</t>
+          <t>emergency_exit_signs</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fire Hydrants</t>
+          <t>Emergency Exit Signs</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>fire_alarm_system</t>
+          <t>emergency_contact_info</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fire Alarm System</t>
+          <t>Emergency Contact Info</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>fire_alarm_system</t>
+          <t>inspection_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Fire Alarm System</t>
+          <t>Inspection Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,40 +745,40 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>emergency_exit_paths</t>
+          <t>inspection_time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Emergency Exit Paths</t>
+          <t>Inspection Time</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>emergency_exit_paths</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Emergency Exit Paths</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -791,23 +791,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>emergency_exit_signs</t>
+          <t>emergency_exit_paths_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Emergency Exit Signs</t>
+          <t>Emergency Exit Paths 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -819,18 +819,18 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>emergency_exit_signs</t>
+          <t>emergency_exit_signs_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emergency Exit Signs</t>
+          <t>Emergency Exit Signs 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -842,246 +842,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>fire_safety_plan</t>
+          <t>comments_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Fire Safety Plan</t>
+          <t>Comments 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>fire_safety_plan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Fire Safety Plan</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>emergency_contact_info</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Emergency Contact Info</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>emergency_contact_info</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Emergency Contact Info</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>inspection_date</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Inspection Date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>inspection_time</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Inspection Time</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>inspector_name</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Inspector Name</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>inspector_name</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Inspector Name</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -1177,663 +947,408 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>fire_stations_choices</t>
+          <t>fire_extinguishers_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>station_1</t>
+          <t>type_1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Station 1</t>
+          <t>Type 1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>fire_stations_choices</t>
+          <t>fire_extinguishers_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>station_2</t>
+          <t>type_2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Station 2</t>
+          <t>Type 2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>fire_stations_choices</t>
+          <t>fire_extinguishers_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>station_3</t>
+          <t>type_3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Station 3</t>
+          <t>Type 3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>fire_extinguishers_choices</t>
+          <t>fire_hydrants_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>type_1</t>
+          <t>hydrant_1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Type 1</t>
+          <t>Hydrant 1</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>fire_extinguishers_choices</t>
+          <t>fire_hydrants_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>type_2</t>
+          <t>hydrant_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Type 2</t>
+          <t>Hydrant 2</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>fire_extinguishers_choices</t>
+          <t>fire_hydrants_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>type_3</t>
+          <t>hydrant_3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>Hydrant 3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>fire_extinguishers_choices</t>
+          <t>fire_alarm_system_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>type_1</t>
+          <t>system_1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Type 1</t>
+          <t>System 1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>fire_extinguishers_choices</t>
+          <t>fire_alarm_system_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>type_2</t>
+          <t>system_2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Type 2</t>
+          <t>System 2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>fire_extinguishers_choices</t>
+          <t>fire_alarm_system_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>type_3</t>
+          <t>system_3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Type 3</t>
+          <t>System 3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>fire_hydrants_choices</t>
+          <t>emergency_exit_paths_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hydrant_1</t>
+          <t>path_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Hydrant 1</t>
+          <t>Path 1</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>fire_hydrants_choices</t>
+          <t>emergency_exit_paths_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>hydrant_2</t>
+          <t>path_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hydrant 2</t>
+          <t>Path 2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>fire_hydrants_choices</t>
+          <t>emergency_exit_paths_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>hydrant_3</t>
+          <t>path_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hydrant 3</t>
+          <t>Path 3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>fire_hydrants_choices</t>
+          <t>emergency_exit_signs_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hydrant_1</t>
+          <t>sign_1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Hydrant 1</t>
+          <t>Sign 1</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fire_hydrants_choices</t>
+          <t>emergency_exit_signs_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hydrant_2</t>
+          <t>sign_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hydrant 2</t>
+          <t>Sign 2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>fire_hydrants_choices</t>
+          <t>emergency_exit_signs_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hydrant_3</t>
+          <t>sign_3</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hydrant 3</t>
+          <t>Sign 3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>fire_alarm_system_choices</t>
+          <t>emergency_contact_info_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>system_1</t>
+          <t>contact_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>System 1</t>
+          <t>Contact 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>fire_alarm_system_choices</t>
+          <t>emergency_contact_info_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>system_2</t>
+          <t>contact_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>System 2</t>
+          <t>Contact 2</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fire_alarm_system_choices</t>
+          <t>emergency_contact_info_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>system_3</t>
+          <t>contact_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>System 3</t>
+          <t>Contact 3</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>fire_alarm_system_choices</t>
+          <t>emergency_exit_paths_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>system_1</t>
+          <t>path_1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>System 1</t>
+          <t>Path 1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>fire_alarm_system_choices</t>
+          <t>emergency_exit_paths_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>system_2</t>
+          <t>path_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>System 2</t>
+          <t>Path 2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>fire_alarm_system_choices</t>
+          <t>emergency_exit_paths_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>system_3</t>
+          <t>path_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>System 3</t>
+          <t>Path 3</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>emergency_exit_paths_choices</t>
+          <t>emergency_exit_signs_2_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>path_1</t>
+          <t>sign_1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Path 1</t>
+          <t>Sign 1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>emergency_exit_paths_choices</t>
+          <t>emergency_exit_signs_2_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>path_2</t>
+          <t>sign_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Path 2</t>
+          <t>Sign 2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>emergency_exit_paths_choices</t>
+          <t>emergency_exit_signs_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>path_3</t>
+          <t>sign_3</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Path 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>emergency_exit_paths_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>path_1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Path 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>emergency_exit_paths_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>path_2</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Path 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>emergency_exit_paths_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>path_3</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Path 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>sign_1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Sign 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>sign_2</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Sign 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>sign_3</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
           <t>Sign 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>sign_1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Sign 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>sign_2</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Sign 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>emergency_exit_signs_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>sign_3</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Sign 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>emergency_contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>contact_1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Contact 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>emergency_contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>contact_2</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Contact 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>emergency_contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>contact_3</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Contact 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>emergency_contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>contact_1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Contact 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>emergency_contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>contact_2</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Contact 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>emergency_contact_info_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>contact_3</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Contact 3</t>
         </is>
       </c>
     </row>
